--- a/resultados_comparacion.xlsx
+++ b/resultados_comparacion.xlsx
@@ -10,8 +10,7 @@
     <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Por_agente" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="P2P_horario" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Glim_y_D" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Metricas_extra" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Metricas_extra" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +427,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Ganancia_neta_$</t>
+          <t>Ganancia_neta_COP</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -454,16 +453,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-307653.2978702479</v>
+        <v>-172034.1286341703</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08290386291157728</v>
+        <v>0.1126722937529999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.248081352303794</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1823462819650881</v>
+        <v>0.1005706430176205</v>
       </c>
     </row>
     <row r="3">
@@ -473,7 +472,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-2317310.668117511</v>
+        <v>-1190254.176184456</v>
       </c>
       <c r="C3" t="n">
         <v>0.08849131417298814</v>
@@ -492,7 +491,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>256054.0379206718</v>
+        <v>145202.5134603907</v>
       </c>
       <c r="C4" t="n">
         <v>0.08849131417298814</v>
@@ -511,7 +510,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2317310.668117511</v>
+        <v>-1190254.176184456</v>
       </c>
       <c r="C5" t="n">
         <v>0.08849131417298814</v>
@@ -530,7 +529,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-2323536.67014065</v>
+        <v>-1208239.068473138</v>
       </c>
       <c r="C6" t="n">
         <v>0.08849131417298814</v>
@@ -595,19 +594,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>87650.85635008519</v>
+        <v>35280.40323059244</v>
       </c>
       <c r="C2" t="n">
-        <v>-119471.9806555221</v>
+        <v>-47378.05870422177</v>
       </c>
       <c r="D2" t="n">
-        <v>56433.85310261038</v>
+        <v>41400.01735499882</v>
       </c>
       <c r="E2" t="n">
-        <v>-119471.9806555221</v>
+        <v>-47378.05870422177</v>
       </c>
       <c r="F2" t="n">
-        <v>-125697.9826786606</v>
+        <v>-65362.95099290348</v>
       </c>
     </row>
     <row r="3">
@@ -617,19 +616,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9145.846886303094</v>
+        <v>2129.70064384634</v>
       </c>
       <c r="C3" t="n">
-        <v>-307168.2011066798</v>
+        <v>-159727.4645754735</v>
       </c>
       <c r="D3" t="n">
-        <v>52990.37979131094</v>
+        <v>27554.99749148169</v>
       </c>
       <c r="E3" t="n">
-        <v>-307168.2011066798</v>
+        <v>-159727.4645754735</v>
       </c>
       <c r="F3" t="n">
-        <v>-307168.2011066798</v>
+        <v>-159727.4645754735</v>
       </c>
     </row>
     <row r="4">
@@ -639,19 +638,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-379258.6758639824</v>
+        <v>-196636.6155976281</v>
       </c>
       <c r="C4" t="n">
-        <v>-1129197.771921448</v>
+        <v>-587182.8413991529</v>
       </c>
       <c r="D4" t="n">
-        <v>66689.49754602092</v>
+        <v>34678.53872393088</v>
       </c>
       <c r="E4" t="n">
-        <v>-1129197.771921448</v>
+        <v>-587182.8413991529</v>
       </c>
       <c r="F4" t="n">
-        <v>-1129197.771921448</v>
+        <v>-587182.8413991529</v>
       </c>
     </row>
     <row r="5">
@@ -661,19 +660,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-12925.27981657288</v>
+        <v>-6430.136715379046</v>
       </c>
       <c r="C5" t="n">
-        <v>-549214.4422746776</v>
+        <v>-285591.5099828324</v>
       </c>
       <c r="D5" t="n">
-        <v>50559.65781808565</v>
+        <v>26291.02206540454</v>
       </c>
       <c r="E5" t="n">
-        <v>-549214.4422746776</v>
+        <v>-285591.5099828324</v>
       </c>
       <c r="F5" t="n">
-        <v>-549214.4422746776</v>
+        <v>-285591.5099828324</v>
       </c>
     </row>
     <row r="6">
@@ -683,19 +682,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-12266.04542608088</v>
+        <v>-6377.480195601904</v>
       </c>
       <c r="C6" t="n">
-        <v>-212258.272159184</v>
+        <v>-110374.3015227757</v>
       </c>
       <c r="D6" t="n">
-        <v>29380.64966264387</v>
+        <v>15277.93782457481</v>
       </c>
       <c r="E6" t="n">
-        <v>-212258.272159184</v>
+        <v>-110374.3015227757</v>
       </c>
       <c r="F6" t="n">
-        <v>-212258.272159184</v>
+        <v>-110374.3015227757</v>
       </c>
     </row>
   </sheetData>
@@ -709,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -758,16 +757,6 @@
           <t>Wi</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Vendedores</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Compradores</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,16 +786,6 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>[1, 2, 3, 4, 5]</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -836,16 +815,6 @@
       <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>[1, 2, 3, 4, 5]</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -875,16 +844,6 @@
       <c r="I4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>[1, 2, 3, 4, 5]</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -914,16 +873,6 @@
       <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>[1, 2, 3, 4, 5]</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -953,16 +902,6 @@
       <c r="I6" t="n">
         <v>0</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>[1, 2, 3, 4, 5]</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -992,16 +931,6 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>[1, 2, 3, 4, 5]</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1031,16 +960,6 @@
       <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>[1, 2, 3, 4, 5]</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1070,16 +989,6 @@
       <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>[1, 2, 3, 4, 5]</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1109,54 +1018,34 @@
       <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>[1, 2, 3, 4, 5]</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3.532530847396926</v>
+        <v>3.532530847396927</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02951727255898622</v>
+        <v>0.2306358242409365</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1279821669340954</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.368605938109474</v>
+        <v>0.3540544471404022</v>
       </c>
       <c r="F11" t="n">
-        <v>31.5697030945263</v>
+        <v>67.70272235702011</v>
       </c>
       <c r="G11" t="n">
-        <v>68.43029690547368</v>
+        <v>32.29727764297989</v>
       </c>
       <c r="H11" t="n">
-        <v>3092.530499683785</v>
+        <v>1248.167016537518</v>
       </c>
       <c r="I11" t="n">
-        <v>768.5553035418216</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>[1]</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>[2, 3, 4, 5]</t>
-        </is>
+        <v>1289.840764638971</v>
       </c>
     </row>
     <row r="12">
@@ -1164,38 +1053,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>8.26665000624463</v>
+        <v>8.266650006244637</v>
       </c>
       <c r="C12" t="n">
-        <v>0.07610525491616955</v>
+        <v>0.3033029825583616</v>
       </c>
       <c r="D12" t="n">
-        <v>0.250921551361683</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1485714363729751</v>
+        <v>0.05872976763949158</v>
       </c>
       <c r="F12" t="n">
-        <v>57.42857181864876</v>
+        <v>52.93648838197458</v>
       </c>
       <c r="G12" t="n">
-        <v>42.57142818135125</v>
+        <v>47.06351161802542</v>
       </c>
       <c r="H12" t="n">
-        <v>3708.778179744563</v>
+        <v>2272.725243065052</v>
       </c>
       <c r="I12" t="n">
-        <v>542.2479567142213</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>[1]</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>[2, 3, 4, 5]</t>
-        </is>
+        <v>897.9514632316118</v>
       </c>
     </row>
     <row r="13">
@@ -1206,35 +1085,25 @@
         <v>10.11358862402805</v>
       </c>
       <c r="C13" t="n">
-        <v>0.09872783419310827</v>
+        <v>0.3322949008468301</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2971090857593883</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3113854996575709</v>
+        <v>0.07404435615770634</v>
       </c>
       <c r="F13" t="n">
-        <v>34.43072501712145</v>
+        <v>53.70221780788532</v>
       </c>
       <c r="G13" t="n">
-        <v>65.56927498287855</v>
+        <v>46.29778219211468</v>
       </c>
       <c r="H13" t="n">
-        <v>6968.059054954766</v>
+        <v>2540.277671190022</v>
       </c>
       <c r="I13" t="n">
-        <v>-527.9459286135527</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>[1]</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>[2, 3, 4, 5]</t>
-        </is>
+        <v>708.6603043369869</v>
       </c>
     </row>
     <row r="14">
@@ -1245,35 +1114,25 @@
         <v>11.59034282110254</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1347137022296338</v>
+        <v>0.3938301517104428</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3420604076263816</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2629340689389659</v>
+        <v>0.08509424475202798</v>
       </c>
       <c r="F14" t="n">
-        <v>36.8532965530517</v>
+        <v>54.2547122376014</v>
       </c>
       <c r="G14" t="n">
-        <v>63.1467034469483</v>
+        <v>45.7452877623986</v>
       </c>
       <c r="H14" t="n">
-        <v>7487.361908632965</v>
+        <v>2708.327600756678</v>
       </c>
       <c r="I14" t="n">
-        <v>-829.7938619261045</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>[1]</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>[2, 3, 4, 5]</t>
-        </is>
+        <v>498.7760579816284</v>
       </c>
     </row>
     <row r="15">
@@ -1281,38 +1140,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>11.38772509545865</v>
+        <v>11.38772509545866</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1446435846788414</v>
+        <v>0.4111881536261818</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3517698246003929</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2629477260376736</v>
+        <v>0.08634934196440314</v>
       </c>
       <c r="F15" t="n">
-        <v>36.85261369811632</v>
+        <v>54.31746709822016</v>
       </c>
       <c r="G15" t="n">
-        <v>63.14738630188368</v>
+        <v>45.68253290177984</v>
       </c>
       <c r="H15" t="n">
-        <v>7349.789214056603</v>
+        <v>2651.567580528671</v>
       </c>
       <c r="I15" t="n">
-        <v>-894.7613555118714</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>[1]</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>[2, 3, 4, 5]</t>
-        </is>
+        <v>411.4029537751998</v>
       </c>
     </row>
     <row r="16">
@@ -1323,35 +1172,25 @@
         <v>7.842862055010452</v>
       </c>
       <c r="C16" t="n">
-        <v>0.07983746913529721</v>
+        <v>0.2878037006788998</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2774025106243203</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2733216854467858</v>
+        <v>0.0827356549436192</v>
       </c>
       <c r="F16" t="n">
-        <v>36.33391572766071</v>
+        <v>54.13678274718096</v>
       </c>
       <c r="G16" t="n">
-        <v>63.66608427233929</v>
+        <v>45.86321725281904</v>
       </c>
       <c r="H16" t="n">
-        <v>5317.649655834213</v>
+        <v>2040.958251991993</v>
       </c>
       <c r="I16" t="n">
-        <v>-249.8489064843577</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>[1]</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>[2, 3, 4, 5]</t>
-        </is>
+        <v>662.0156144141301</v>
       </c>
     </row>
     <row r="17">
@@ -1362,35 +1201,25 @@
         <v>1.880353385306708</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0167819226690045</v>
+        <v>0.1878771421528856</v>
       </c>
       <c r="D17" t="n">
-        <v>0.08932391922029639</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0.05419950806187848</v>
+        <v>-0.03701331147430717</v>
       </c>
       <c r="F17" t="n">
-        <v>52.70997540309393</v>
+        <v>48.14933442628465</v>
       </c>
       <c r="G17" t="n">
-        <v>47.29002459690608</v>
+        <v>51.85066557371536</v>
       </c>
       <c r="H17" t="n">
-        <v>1432.533694065656</v>
+        <v>1038.39805437462</v>
       </c>
       <c r="I17" t="n">
-        <v>934.9051267388943</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>[1]</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>[2, 3, 4, 5]</t>
-        </is>
+        <v>1036.064087558717</v>
       </c>
     </row>
     <row r="18">
@@ -1421,16 +1250,6 @@
       <c r="I18" t="n">
         <v>0</v>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>[1, 2, 3, 4, 5]</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1460,16 +1279,6 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>[1, 2, 3, 4, 5]</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1499,16 +1308,6 @@
       <c r="I20" t="n">
         <v>0</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>[1, 2, 3, 4, 5]</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1538,16 +1337,6 @@
       <c r="I21" t="n">
         <v>0</v>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>[1, 2, 3, 4, 5]</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1577,16 +1366,6 @@
       <c r="I22" t="n">
         <v>0</v>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>[1, 2, 3, 4, 5]</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1616,16 +1395,6 @@
       <c r="I23" t="n">
         <v>0</v>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>[1, 2, 3, 4, 5]</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1655,16 +1424,6 @@
       <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>[1, 2, 3, 4, 5]</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1693,16 +1452,6 @@
       </c>
       <c r="I25" t="n">
         <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>[1, 2, 3, 4, 5]</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -1716,946 +1465,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Hora</t>
+          <t>PoF_P2P_vs_C4</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Gklim_A1</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Gklim_A2</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Gklim_A3</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Gklim_A4</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Gklim_A5</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>D_A1</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>D_A2</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>D_A3</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>D_A4</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>D_A5</t>
+          <t>Spread_C4_kWh</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>8.06709654637311</v>
-      </c>
-      <c r="H2" t="n">
-        <v>12.78475410852714</v>
-      </c>
-      <c r="I2" t="n">
-        <v>17.47382095696338</v>
-      </c>
-      <c r="J2" t="n">
-        <v>24.62006449510046</v>
-      </c>
-      <c r="K2" t="n">
-        <v>7.609248773055333</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>8.026645581105617</v>
-      </c>
-      <c r="H3" t="n">
-        <v>12.92171406104061</v>
-      </c>
-      <c r="I3" t="n">
-        <v>17.52057637694895</v>
-      </c>
-      <c r="J3" t="n">
-        <v>22.87329883242588</v>
-      </c>
-      <c r="K3" t="n">
-        <v>7.654495777277652</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>7.980303132048048</v>
-      </c>
-      <c r="H4" t="n">
-        <v>12.73208139000268</v>
-      </c>
-      <c r="I4" t="n">
-        <v>17.50464775700278</v>
-      </c>
-      <c r="J4" t="n">
-        <v>22.23357009748736</v>
-      </c>
-      <c r="K4" t="n">
-        <v>7.631186976744182</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>7.924094523554017</v>
-      </c>
-      <c r="H5" t="n">
-        <v>12.95463631229236</v>
-      </c>
-      <c r="I5" t="n">
-        <v>17.48641445213968</v>
-      </c>
-      <c r="J5" t="n">
-        <v>21.80020446620238</v>
-      </c>
-      <c r="K5" t="n">
-        <v>7.65731860465116</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7.895224413641539</v>
-      </c>
-      <c r="H6" t="n">
-        <v>12.84831317829457</v>
-      </c>
-      <c r="I6" t="n">
-        <v>19.76481964715318</v>
-      </c>
-      <c r="J6" t="n">
-        <v>21.27555015248413</v>
-      </c>
-      <c r="K6" t="n">
-        <v>7.661364186046513</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.001022631483931941</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.000898701203037728</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.001099233210929518</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.0004044109378993099</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.001048658421681678</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8.166828276542176</v>
-      </c>
-      <c r="H7" t="n">
-        <v>12.98616372093024</v>
-      </c>
-      <c r="I7" t="n">
-        <v>25.03879445946462</v>
-      </c>
-      <c r="J7" t="n">
-        <v>21.98421223298928</v>
-      </c>
-      <c r="K7" t="n">
-        <v>7.770785227021041</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.6286944333554149</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.2899600347153516</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.3533636453395672</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.2405230743201674</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.2210994629014396</v>
-      </c>
-      <c r="G8" t="n">
-        <v>8.578612963240808</v>
-      </c>
-      <c r="H8" t="n">
-        <v>12.43472246242932</v>
-      </c>
-      <c r="I8" t="n">
-        <v>31.93381226286677</v>
-      </c>
-      <c r="J8" t="n">
-        <v>22.99979324866269</v>
-      </c>
-      <c r="K8" t="n">
-        <v>8.12026277712285</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3.392861787916555</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.38625108438029</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.964410654519743</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.229167404437316</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.9359737068460102</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5.733310258100238</v>
-      </c>
-      <c r="H9" t="n">
-        <v>16.68046070167163</v>
-      </c>
-      <c r="I9" t="n">
-        <v>56.94129068927329</v>
-      </c>
-      <c r="J9" t="n">
-        <v>22.70471508283503</v>
-      </c>
-      <c r="K9" t="n">
-        <v>10.66693682488767</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="n">
-        <v>7.036124152719627</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.010800688197128</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4.088676418312903</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2.923504631020172</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1.986756835931006</v>
-      </c>
-      <c r="G10" t="n">
-        <v>7.731796158867305</v>
-      </c>
-      <c r="H10" t="n">
-        <v>19.12457678112318</v>
-      </c>
-      <c r="I10" t="n">
-        <v>67.36414668050465</v>
-      </c>
-      <c r="J10" t="n">
-        <v>20.2143437534511</v>
-      </c>
-      <c r="K10" t="n">
-        <v>11.01022559611813</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="n">
-        <v>10.06318443431709</v>
-      </c>
-      <c r="C11" t="n">
-        <v>4.572909798373241</v>
-      </c>
-      <c r="D11" t="n">
-        <v>5.804654369622628</v>
-      </c>
-      <c r="E11" t="n">
-        <v>4.636965709074326</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2.524028431537276</v>
-      </c>
-      <c r="G11" t="n">
-        <v>6.530653586920159</v>
-      </c>
-      <c r="H11" t="n">
-        <v>17.31140937258946</v>
-      </c>
-      <c r="I11" t="n">
-        <v>68.45317257417804</v>
-      </c>
-      <c r="J11" t="n">
-        <v>16.42529805484986</v>
-      </c>
-      <c r="K11" t="n">
-        <v>10.95620281512743</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="n">
-        <v>12.12661101999013</v>
-      </c>
-      <c r="C12" t="n">
-        <v>5.630270794974605</v>
-      </c>
-      <c r="D12" t="n">
-        <v>6.967335503964091</v>
-      </c>
-      <c r="E12" t="n">
-        <v>5.528039699581514</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2.69290038779362</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3.8599610137455</v>
-      </c>
-      <c r="H12" t="n">
-        <v>14.32185742976477</v>
-      </c>
-      <c r="I12" t="n">
-        <v>66.29584216142673</v>
-      </c>
-      <c r="J12" t="n">
-        <v>13.57982725689707</v>
-      </c>
-      <c r="K12" t="n">
-        <v>10.56378954339109</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="n">
-        <v>12.66159450049717</v>
-      </c>
-      <c r="C13" t="n">
-        <v>5.834293128524332</v>
-      </c>
-      <c r="D13" t="n">
-        <v>7.019203023184827</v>
-      </c>
-      <c r="E13" t="n">
-        <v>5.588320902356133</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2.936572777045865</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2.548005876469118</v>
-      </c>
-      <c r="H13" t="n">
-        <v>13.72683897994341</v>
-      </c>
-      <c r="I13" t="n">
-        <v>63.02956328382864</v>
-      </c>
-      <c r="J13" t="n">
-        <v>12.80831371023791</v>
-      </c>
-      <c r="K13" t="n">
-        <v>10.32635935377604</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="n">
-        <v>12.68741612442837</v>
-      </c>
-      <c r="C14" t="n">
-        <v>5.75439754976857</v>
-      </c>
-      <c r="D14" t="n">
-        <v>7.030842580053824</v>
-      </c>
-      <c r="E14" t="n">
-        <v>5.521559748416959</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2.889690356241221</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.097073303325832</v>
-      </c>
-      <c r="H14" t="n">
-        <v>11.0584876278507</v>
-      </c>
-      <c r="I14" t="n">
-        <v>51.10449205973865</v>
-      </c>
-      <c r="J14" t="n">
-        <v>12.45310249595366</v>
-      </c>
-      <c r="K14" t="n">
-        <v>10.3236962162012</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="n">
-        <v>12.39710162822821</v>
-      </c>
-      <c r="C15" t="n">
-        <v>5.312320084222242</v>
-      </c>
-      <c r="D15" t="n">
-        <v>6.790537627431112</v>
-      </c>
-      <c r="E15" t="n">
-        <v>5.110569902329693</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2.762131228012402</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.009376532769556</v>
-      </c>
-      <c r="H15" t="n">
-        <v>10.18318467392187</v>
-      </c>
-      <c r="I15" t="n">
-        <v>44.62765128289493</v>
-      </c>
-      <c r="J15" t="n">
-        <v>13.19404961733708</v>
-      </c>
-      <c r="K15" t="n">
-        <v>9.715293170231261</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="n">
-        <v>10.66997447425497</v>
-      </c>
-      <c r="C16" t="n">
-        <v>4.701674427271414</v>
-      </c>
-      <c r="D16" t="n">
-        <v>5.909410572502209</v>
-      </c>
-      <c r="E16" t="n">
-        <v>4.359066434744975</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2.63237255333248</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2.827112419244517</v>
-      </c>
-      <c r="H16" t="n">
-        <v>13.10427944773461</v>
-      </c>
-      <c r="I16" t="n">
-        <v>56.36387492891079</v>
-      </c>
-      <c r="J16" t="n">
-        <v>15.72049157997393</v>
-      </c>
-      <c r="K16" t="n">
-        <v>10.21959577494825</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="n">
-        <v>7.797810821636229</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.591117198228128</v>
-      </c>
-      <c r="D17" t="n">
-        <v>4.413288234821771</v>
-      </c>
-      <c r="E17" t="n">
-        <v>3.18503830564784</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2.063695753089466</v>
-      </c>
-      <c r="G17" t="n">
-        <v>5.917457436329522</v>
-      </c>
-      <c r="H17" t="n">
-        <v>14.27278972314507</v>
-      </c>
-      <c r="I17" t="n">
-        <v>62.34014937022884</v>
-      </c>
-      <c r="J17" t="n">
-        <v>19.0410676912932</v>
-      </c>
-      <c r="K17" t="n">
-        <v>10.47489795058226</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="n">
-        <v>4.271147091438997</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1.878519501279261</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2.417543169333141</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1.702809089624624</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1.418797000801925</v>
-      </c>
-      <c r="G18" t="n">
-        <v>11.322867726768</v>
-      </c>
-      <c r="H18" t="n">
-        <v>13.18982690648032</v>
-      </c>
-      <c r="I18" t="n">
-        <v>65.97789848567416</v>
-      </c>
-      <c r="J18" t="n">
-        <v>22.12622243593491</v>
-      </c>
-      <c r="K18" t="n">
-        <v>10.44250179068495</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="n">
-        <v>1.033164265487491</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.4232677894566007</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.582125582408593</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.4158482484099403</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.431380049613002</v>
-      </c>
-      <c r="G19" t="n">
-        <v>17.83633772042216</v>
-      </c>
-      <c r="H19" t="n">
-        <v>14.55512338956352</v>
-      </c>
-      <c r="I19" t="n">
-        <v>65.76363078452511</v>
-      </c>
-      <c r="J19" t="n">
-        <v>25.43053319209593</v>
-      </c>
-      <c r="K19" t="n">
-        <v>10.76139766420836</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.01362633237131063</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.005623052454548884</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.009107422111403493</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.005908693566966069</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.008072528547700051</v>
-      </c>
-      <c r="G20" t="n">
-        <v>14.5196086871718</v>
-      </c>
-      <c r="H20" t="n">
-        <v>14.59366336273724</v>
-      </c>
-      <c r="I20" t="n">
-        <v>56.19094796864023</v>
-      </c>
-      <c r="J20" t="n">
-        <v>28.19798187325956</v>
-      </c>
-      <c r="K20" t="n">
-        <v>8.603212285485165</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>10.21466347035735</v>
-      </c>
-      <c r="H21" t="n">
-        <v>14.36020464581663</v>
-      </c>
-      <c r="I21" t="n">
-        <v>44.2717366598524</v>
-      </c>
-      <c r="J21" t="n">
-        <v>28.86605217851862</v>
-      </c>
-      <c r="K21" t="n">
-        <v>7.988064584717608</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>8.819856607889145</v>
-      </c>
-      <c r="H22" t="n">
-        <v>14.3255283614007</v>
-      </c>
-      <c r="I22" t="n">
-        <v>34.33577300810837</v>
-      </c>
-      <c r="J22" t="n">
-        <v>28.82010708740188</v>
-      </c>
-      <c r="K22" t="n">
-        <v>7.743706998128843</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>8.282874042841382</v>
-      </c>
-      <c r="H23" t="n">
-        <v>13.95489227593845</v>
-      </c>
-      <c r="I23" t="n">
-        <v>24.1880991027366</v>
-      </c>
-      <c r="J23" t="n">
-        <v>28.84305524567241</v>
-      </c>
-      <c r="K23" t="n">
-        <v>7.688692746782758</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>8.028618962537092</v>
-      </c>
-      <c r="H24" t="n">
-        <v>13.28332852713179</v>
-      </c>
-      <c r="I24" t="n">
-        <v>18.56146960667506</v>
-      </c>
-      <c r="J24" t="n">
-        <v>27.42588994370897</v>
-      </c>
-      <c r="K24" t="n">
-        <v>7.587087596899228</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>7.972568629819503</v>
-      </c>
-      <c r="H25" t="n">
-        <v>12.81033111111111</v>
-      </c>
-      <c r="I25" t="n">
-        <v>17.52878905105587</v>
-      </c>
-      <c r="J25" t="n">
-        <v>26.6292616039057</v>
-      </c>
-      <c r="K25" t="n">
-        <v>7.639333953488372</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>PoF_P2P_vs_C4</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Spread_C4_kWh</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>pi_ppa</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>6.552451692296165</v>
+        <v>6.02325217714476</v>
       </c>
       <c r="B2" t="n">
         <v>20.3411259094923</v>
-      </c>
-      <c r="C2" t="n">
-        <v>682</v>
       </c>
     </row>
   </sheetData>

--- a/resultados_comparacion.xlsx
+++ b/resultados_comparacion.xlsx
@@ -462,7 +462,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1005706430176205</v>
+        <v>0.09843861618797374</v>
       </c>
     </row>
     <row r="3">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1190254.176184456</v>
+        <v>-1199097.222712494</v>
       </c>
       <c r="C3" t="n">
         <v>0.08849131417298814</v>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1190254.176184456</v>
+        <v>-1199097.222712494</v>
       </c>
       <c r="C5" t="n">
         <v>0.08849131417298814</v>
@@ -594,16 +594,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35280.40323059244</v>
+        <v>35291.75670253135</v>
       </c>
       <c r="C2" t="n">
-        <v>-47378.05870422177</v>
+        <v>-56221.10523225918</v>
       </c>
       <c r="D2" t="n">
         <v>41400.01735499882</v>
       </c>
       <c r="E2" t="n">
-        <v>-47378.05870422177</v>
+        <v>-56221.10523225918</v>
       </c>
       <c r="F2" t="n">
         <v>-65362.95099290348</v>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2129.70064384634</v>
+        <v>2128.120044199041</v>
       </c>
       <c r="C3" t="n">
         <v>-159727.4645754735</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-196636.6155976281</v>
+        <v>-196635.1040959009</v>
       </c>
       <c r="C4" t="n">
         <v>-587182.8413991529</v>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-6430.136715379046</v>
+        <v>-6434.741175812252</v>
       </c>
       <c r="C5" t="n">
         <v>-285591.5099828324</v>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-6377.480195601904</v>
+        <v>-6384.160109187535</v>
       </c>
       <c r="C6" t="n">
         <v>-110374.3015227757</v>
@@ -1024,7 +1024,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3.532530847396927</v>
+        <v>3.532530847396926</v>
       </c>
       <c r="C11" t="n">
         <v>0.2306358242409365</v>
@@ -1033,19 +1033,19 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3540544471404022</v>
+        <v>0.3475081921331418</v>
       </c>
       <c r="F11" t="n">
-        <v>67.70272235702011</v>
+        <v>67.37540960665709</v>
       </c>
       <c r="G11" t="n">
-        <v>32.29727764297989</v>
+        <v>32.62459039334291</v>
       </c>
       <c r="H11" t="n">
-        <v>1248.167016537518</v>
+        <v>1214.596568577373</v>
       </c>
       <c r="I11" t="n">
-        <v>1289.840764638971</v>
+        <v>1288.557051215283</v>
       </c>
     </row>
     <row r="12">
@@ -1053,7 +1053,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>8.266650006244637</v>
+        <v>8.266650006244632</v>
       </c>
       <c r="C12" t="n">
         <v>0.3033029825583616</v>
@@ -1062,19 +1062,19 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05872976763949158</v>
+        <v>0.05771610830694621</v>
       </c>
       <c r="F12" t="n">
-        <v>52.93648838197458</v>
+        <v>52.88580541534731</v>
       </c>
       <c r="G12" t="n">
-        <v>47.06351161802542</v>
+        <v>47.11419458465269</v>
       </c>
       <c r="H12" t="n">
-        <v>2272.725243065052</v>
+        <v>2185.704212879771</v>
       </c>
       <c r="I12" t="n">
-        <v>897.9514632316118</v>
+        <v>897.4863009012026</v>
       </c>
     </row>
     <row r="13">
@@ -1091,19 +1091,19 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07404435615770634</v>
+        <v>0.07296110266069925</v>
       </c>
       <c r="F13" t="n">
-        <v>53.70221780788532</v>
+        <v>53.64805513303496</v>
       </c>
       <c r="G13" t="n">
-        <v>46.29778219211468</v>
+        <v>46.35194486696503</v>
       </c>
       <c r="H13" t="n">
-        <v>2540.277671190022</v>
+        <v>2433.944575420626</v>
       </c>
       <c r="I13" t="n">
-        <v>708.6603043369869</v>
+        <v>708.0521436430777</v>
       </c>
     </row>
     <row r="14">
@@ -1120,19 +1120,19 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.08509424475202798</v>
+        <v>0.08476834375330757</v>
       </c>
       <c r="F14" t="n">
-        <v>54.2547122376014</v>
+        <v>54.23841718766538</v>
       </c>
       <c r="G14" t="n">
-        <v>45.7452877623986</v>
+        <v>45.76158281233463</v>
       </c>
       <c r="H14" t="n">
-        <v>2708.327600756678</v>
+        <v>2584.844157540534</v>
       </c>
       <c r="I14" t="n">
-        <v>498.7760579816284</v>
+        <v>498.5663741535215</v>
       </c>
     </row>
     <row r="15">
@@ -1149,19 +1149,19 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.08634934196440314</v>
+        <v>0.08634472813822337</v>
       </c>
       <c r="F15" t="n">
-        <v>54.31746709822016</v>
+        <v>54.31723640691116</v>
       </c>
       <c r="G15" t="n">
-        <v>45.68253290177984</v>
+        <v>45.68276359308883</v>
       </c>
       <c r="H15" t="n">
-        <v>2651.567580528671</v>
+        <v>2529.565960302258</v>
       </c>
       <c r="I15" t="n">
-        <v>411.4029537751998</v>
+        <v>411.4000371463512</v>
       </c>
     </row>
     <row r="16">
@@ -1178,19 +1178,19 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0827356549436192</v>
+        <v>0.08208303939135925</v>
       </c>
       <c r="F16" t="n">
-        <v>54.13678274718096</v>
+        <v>54.10415196956796</v>
       </c>
       <c r="G16" t="n">
-        <v>45.86321725281904</v>
+        <v>45.89584803043203</v>
       </c>
       <c r="H16" t="n">
-        <v>2040.958251991993</v>
+        <v>1957.874486260877</v>
       </c>
       <c r="I16" t="n">
-        <v>662.0156144141301</v>
+        <v>661.7314858090822</v>
       </c>
     </row>
     <row r="17">
@@ -1207,19 +1207,19 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.03701331147430717</v>
+        <v>-0.04231120106786132</v>
       </c>
       <c r="F17" t="n">
-        <v>48.14933442628465</v>
+        <v>47.88443994660693</v>
       </c>
       <c r="G17" t="n">
-        <v>51.85066557371536</v>
+        <v>52.11556005339307</v>
       </c>
       <c r="H17" t="n">
-        <v>1038.39805437462</v>
+        <v>1020.09436331758</v>
       </c>
       <c r="I17" t="n">
-        <v>1036.064087558717</v>
+        <v>1035.511030901784</v>
       </c>
     </row>
     <row r="18">
@@ -1482,7 +1482,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6.02325217714476</v>
+        <v>6.023252177144759</v>
       </c>
       <c r="B2" t="n">
         <v>20.3411259094923</v>

--- a/resultados_comparacion.xlsx
+++ b/resultados_comparacion.xlsx
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,27 +432,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Escenario</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Ganancia_neta_COP</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Ganancia_neta_$</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>SS</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>IE</t>
         </is>
@@ -453,16 +465,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-172034.1286341703</v>
+        <v>138809.0971821197</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1126722937529999</v>
+        <v>0.8373900438478333</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0.8665001357634031</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09843861618797374</v>
+        <v>-0.1898421814736614</v>
       </c>
     </row>
     <row r="3">
@@ -472,16 +484,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1199097.222712494</v>
+        <v>139838.4852193923</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08849131417298814</v>
+        <v>0.5692712692917075</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7853866396558743</v>
+        <v>0.5890607796826215</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4">
@@ -491,16 +503,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>145202.5134603907</v>
+        <v>112691.4509022053</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08849131417298814</v>
+        <v>0.5692712692917075</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7853866396558743</v>
+        <v>0.5890607796826215</v>
       </c>
       <c r="E4" t="n">
-        <v>-1</v>
+        <v>-0.9328048603245422</v>
       </c>
     </row>
     <row r="5">
@@ -510,16 +522,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1199097.222712494</v>
+        <v>103387.3941828218</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08849131417298814</v>
+        <v>0.5692712692917075</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7853866396558743</v>
+        <v>0.5890607796826215</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
@@ -529,16 +541,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1208239.068473138</v>
+        <v>108745.1679946647</v>
       </c>
       <c r="C6" t="n">
-        <v>0.08849131417298814</v>
+        <v>0.5692712692917075</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7853866396558743</v>
+        <v>0.5890607796826215</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -552,36 +564,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>P2P</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
@@ -594,19 +606,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35291.75670253135</v>
+        <v>66488.87224966632</v>
       </c>
       <c r="C2" t="n">
-        <v>-56221.10523225918</v>
+        <v>68766.10632519744</v>
       </c>
       <c r="D2" t="n">
-        <v>41400.01735499882</v>
+        <v>63191.25655201568</v>
       </c>
       <c r="E2" t="n">
-        <v>-56221.10523225918</v>
+        <v>62188.22145529254</v>
       </c>
       <c r="F2" t="n">
-        <v>-65362.95099290348</v>
+        <v>62456.66151250518</v>
       </c>
     </row>
     <row r="3">
@@ -616,19 +628,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2128.120044199041</v>
+        <v>19810.00361875292</v>
       </c>
       <c r="C3" t="n">
-        <v>-159727.4645754735</v>
+        <v>22737.72379661772</v>
       </c>
       <c r="D3" t="n">
-        <v>27554.99749148169</v>
+        <v>15887.36880429244</v>
       </c>
       <c r="E3" t="n">
-        <v>-159727.4645754735</v>
+        <v>14044.30996891527</v>
       </c>
       <c r="F3" t="n">
-        <v>-159727.4645754735</v>
+        <v>16174.72141134232</v>
       </c>
     </row>
     <row r="4">
@@ -638,19 +650,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-196635.1040959009</v>
+        <v>12172.28445731253</v>
       </c>
       <c r="C4" t="n">
-        <v>-587182.8413991529</v>
+        <v>15272.55083458049</v>
       </c>
       <c r="D4" t="n">
-        <v>34678.53872393088</v>
+        <v>8343.637726546009</v>
       </c>
       <c r="E4" t="n">
-        <v>-587182.8413991529</v>
+        <v>7788.703903100461</v>
       </c>
       <c r="F4" t="n">
-        <v>-587182.8413991529</v>
+        <v>9289.49723605082</v>
       </c>
     </row>
     <row r="5">
@@ -660,19 +672,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-6434.741175812252</v>
+        <v>35698.66526948559</v>
       </c>
       <c r="C5" t="n">
-        <v>-285591.5099828324</v>
+        <v>33062.10426299669</v>
       </c>
       <c r="D5" t="n">
-        <v>26291.02206540454</v>
+        <v>21483.02892754934</v>
       </c>
       <c r="E5" t="n">
-        <v>-285591.5099828324</v>
+        <v>19366.15885551354</v>
       </c>
       <c r="F5" t="n">
-        <v>-285591.5099828324</v>
+        <v>20824.28783476638</v>
       </c>
     </row>
     <row r="6">
@@ -682,19 +694,41 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-6384.160109187535</v>
+        <v>2568.91097435111</v>
       </c>
       <c r="C6" t="n">
-        <v>-110374.3015227757</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>15277.93782457481</v>
+        <v>2248.76706754619</v>
       </c>
       <c r="E6" t="n">
-        <v>-110374.3015227757</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-110374.3015227757</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2070.360612551229</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1537.391824255647</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -712,47 +746,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>kWh_P2P</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>SS</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>IE</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PS_%</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PSR_%</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Wj</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Wi</t>
         </is>
@@ -763,28 +797,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.5624459457212084</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-0.4999870658893482</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>25.00064670553259</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>74.99935329446741</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>386.2057834806377</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-231.7119547921885</v>
       </c>
     </row>
     <row r="3">
@@ -792,28 +826,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.4885964065546198</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-0.4292189957726532</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>28.53905021136734</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>71.46094978863266</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>312.3301636111426</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-194.3049980419629</v>
       </c>
     </row>
     <row r="4">
@@ -821,28 +855,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.510942873719857</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-0.4292189957726377</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>28.53905021136812</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>71.46094978863188</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>312.3262346915286</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-194.3049980419611</v>
       </c>
     </row>
     <row r="5">
@@ -850,28 +884,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.5373902643481295</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-0.4292189957726379</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>28.53905021136811</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>71.46094978863189</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>312.3197444640236</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-194.3049980419611</v>
       </c>
     </row>
     <row r="6">
@@ -879,28 +913,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.583216524623086</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-0.4999870658900903</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>25.00064670549548</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>74.9993532945045</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>386.2007995714465</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-231.7119547922896</v>
       </c>
     </row>
     <row r="7">
@@ -908,28 +942,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.9484810945203417</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0.866559348766242</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>6.672032561687893</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>93.3279674383121</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>893.5626990292251</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-528.1751824214176</v>
       </c>
     </row>
     <row r="8">
@@ -937,28 +971,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1.044229769881175</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.7742983325936428</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>182.4527354399995</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-304.3097009888528</v>
       </c>
     </row>
     <row r="9">
@@ -966,28 +1000,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.8169625006017113</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.7365441523844599</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>837.5872473204959</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-139.8953544970568</v>
       </c>
     </row>
     <row r="10">
@@ -995,28 +1029,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1.238893016775156</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.7292246311894153</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.1608540987454164</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>58.04270493727082</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>41.95729506272918</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>559.5471120521648</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>128.800735898053</v>
       </c>
     </row>
     <row r="11">
@@ -1024,28 +1058,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3.532530847396926</v>
+        <v>2.417950560127202</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2306358242409365</v>
+        <v>0.857983524411118</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3475081921331418</v>
+        <v>0.4506931797030318</v>
       </c>
       <c r="F11" t="n">
-        <v>67.37540960665709</v>
+        <v>72.53465898515159</v>
       </c>
       <c r="G11" t="n">
-        <v>32.62459039334291</v>
+        <v>27.46534101484841</v>
       </c>
       <c r="H11" t="n">
-        <v>1214.596568577373</v>
+        <v>620.0819227670872</v>
       </c>
       <c r="I11" t="n">
-        <v>1288.557051215283</v>
+        <v>75.76450760779487</v>
       </c>
     </row>
     <row r="12">
@@ -1053,28 +1087,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>8.266650006244632</v>
+        <v>3.133309717572526</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3033029825583616</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0.9440313913561559</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05771610830694621</v>
+        <v>0.7093278258359393</v>
       </c>
       <c r="F12" t="n">
-        <v>52.88580541534731</v>
+        <v>85.46639129179697</v>
       </c>
       <c r="G12" t="n">
-        <v>47.11419458465269</v>
+        <v>14.53360870820303</v>
       </c>
       <c r="H12" t="n">
-        <v>2185.704212879771</v>
+        <v>277.231129021385</v>
       </c>
       <c r="I12" t="n">
-        <v>897.4863009012026</v>
+        <v>150.024275542243</v>
       </c>
     </row>
     <row r="13">
@@ -1082,28 +1116,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>10.11358862402805</v>
+        <v>2.910778247959986</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3322949008468301</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0.8299450522791015</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07296110266069925</v>
+        <v>-0.7252011201764965</v>
       </c>
       <c r="F13" t="n">
-        <v>53.64805513303496</v>
+        <v>13.73994399117517</v>
       </c>
       <c r="G13" t="n">
-        <v>46.35194486696503</v>
+        <v>86.26005600882482</v>
       </c>
       <c r="H13" t="n">
-        <v>2433.944575420626</v>
+        <v>2839.910443724124</v>
       </c>
       <c r="I13" t="n">
-        <v>708.0521436430777</v>
+        <v>-508.3008688358131</v>
       </c>
     </row>
     <row r="14">
@@ -1111,28 +1145,28 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>11.59034282110254</v>
+        <v>2.773646437750525</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3938301517104428</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.7515628027201066</v>
       </c>
       <c r="E14" t="n">
-        <v>0.08476834375330757</v>
+        <v>-0.6399447465724917</v>
       </c>
       <c r="F14" t="n">
-        <v>54.23841718766538</v>
+        <v>18.00276267137542</v>
       </c>
       <c r="G14" t="n">
-        <v>45.76158281233463</v>
+        <v>81.99723732862459</v>
       </c>
       <c r="H14" t="n">
-        <v>2584.844157540534</v>
+        <v>2268.162380454639</v>
       </c>
       <c r="I14" t="n">
-        <v>498.5663741535215</v>
+        <v>-457.6556333437726</v>
       </c>
     </row>
     <row r="15">
@@ -1140,28 +1174,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>11.38772509545866</v>
+        <v>3.032617011177051</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4111881536261818</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0.7804418583307924</v>
       </c>
       <c r="E15" t="n">
-        <v>0.08634472813822337</v>
+        <v>-0.9999719986096078</v>
       </c>
       <c r="F15" t="n">
-        <v>54.31723640691116</v>
+        <v>0.001400069519602803</v>
       </c>
       <c r="G15" t="n">
-        <v>45.68276359308883</v>
+        <v>99.9985999304804</v>
       </c>
       <c r="H15" t="n">
-        <v>2529.565960302258</v>
+        <v>3412.619936526687</v>
       </c>
       <c r="I15" t="n">
-        <v>411.4000371463512</v>
+        <v>-661.4489907695992</v>
       </c>
     </row>
     <row r="16">
@@ -1169,28 +1203,28 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>7.842862055010452</v>
+        <v>3.063083185734643</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2878037006788998</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0.8292485422201399</v>
       </c>
       <c r="E16" t="n">
-        <v>0.08208303939135925</v>
+        <v>0.7025551758308846</v>
       </c>
       <c r="F16" t="n">
-        <v>54.10415196956796</v>
+        <v>85.12775879154422</v>
       </c>
       <c r="G16" t="n">
-        <v>45.89584803043203</v>
+        <v>14.87224120845577</v>
       </c>
       <c r="H16" t="n">
-        <v>1957.874486260877</v>
+        <v>222.2007410035829</v>
       </c>
       <c r="I16" t="n">
-        <v>661.7314858090822</v>
+        <v>139.5404412843162</v>
       </c>
     </row>
     <row r="17">
@@ -1198,28 +1232,28 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>1.880353385306708</v>
+        <v>3.281944431504254</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1878771421528856</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0.9703931355941023</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.04231120106786132</v>
+        <v>0.5999741845716707</v>
       </c>
       <c r="F17" t="n">
-        <v>47.88443994660693</v>
+        <v>79.99870922858354</v>
       </c>
       <c r="G17" t="n">
-        <v>52.11556005339307</v>
+        <v>20.00129077141646</v>
       </c>
       <c r="H17" t="n">
-        <v>1020.09436331758</v>
+        <v>439.6967896917781</v>
       </c>
       <c r="I17" t="n">
-        <v>1035.511030901784</v>
+        <v>81.50814172369971</v>
       </c>
     </row>
     <row r="18">
@@ -1227,28 +1261,28 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1.855773656675085</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.7799942942880668</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.4625121877503209</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>73.12560938751605</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>26.87439061248395</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>489.2809228670089</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>133.321606076177</v>
       </c>
     </row>
     <row r="19">
@@ -1256,28 +1290,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.3727327307205366</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.659082616645565</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>0.2728552497273139</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>63.6427624863657</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>36.3572375136343</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>223.2821850024586</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>379.1092377104039</v>
       </c>
     </row>
     <row r="20">
@@ -1285,28 +1319,28 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.6246943150497889</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.5685501428830233</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-0.08775149855228241</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>45.61242507238588</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>54.38757492761412</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>326.4915965441656</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>145.9036729747903</v>
       </c>
     </row>
     <row r="21">
@@ -1314,28 +1348,28 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>0.877615565053756</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.4427100869313471</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.008121506881702635</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>50.40607534408513</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>49.59392465591487</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>396.8458967453635</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-39.63988449551054</v>
       </c>
     </row>
     <row r="22">
@@ -1343,28 +1377,28 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>0.739566240552067</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.5073270815837161</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.09345895699468423</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>54.67294784973421</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>45.32705215026579</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>298.5738460818336</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>12.07463031357074</v>
       </c>
     </row>
     <row r="23">
@@ -1372,28 +1406,28 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1.14122721723133</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.8054428762131615</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.6461159005504926</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>82.30579502752464</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>17.69420497247537</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>102.4886731393838</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>-107.6218115774053</v>
       </c>
     </row>
     <row r="24">
@@ -1401,28 +1435,28 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>0.9364795040944236</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>-0.5001430068316975</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>24.99284965841513</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>75.00715034158489</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>582.2832380022438</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>-347.5998255914813</v>
       </c>
     </row>
     <row r="25">
@@ -1430,28 +1464,28 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>0.6426310240088519</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>-0.5554777833531442</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>22.22611083234278</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>77.77388916765722</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>470.2012422398208</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>-269.1877668165117</v>
       </c>
     </row>
   </sheetData>
@@ -1469,12 +1503,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>PoF_P2P_vs_C4</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Spread_C4_kWh</t>
         </is>
@@ -1482,10 +1516,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6.023252177144759</v>
+        <v>0.2165847181327795</v>
       </c>
       <c r="B2" t="n">
-        <v>20.3411259094923</v>
+        <v>14.46541230822103</v>
       </c>
     </row>
   </sheetData>

--- a/resultados_comparacion.xlsx
+++ b/resultados_comparacion.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Ganancia_neta_$</t>
+          <t>Ganancia_neta_COP</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -465,16 +465,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>138809.0971821197</v>
+        <v>150117.7782155001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8373900438478333</v>
+        <v>0.1126722937529999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8665001357634031</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1898421814736614</v>
+        <v>0.1510131705234475</v>
       </c>
     </row>
     <row r="3">
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>139838.4852193923</v>
+        <v>165409.7130091735</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5692712692917075</v>
+        <v>0.08849131417298814</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5890607796826215</v>
+        <v>0.7853866396558743</v>
       </c>
       <c r="E3" t="n">
-        <v>-1</v>
+        <v>-0.2628055550044501</v>
       </c>
     </row>
     <row r="4">
@@ -503,16 +503,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112691.4509022053</v>
+        <v>145202.5134603907</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5692712692917075</v>
+        <v>0.08849131417298814</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5890607796826215</v>
+        <v>0.7853866396558743</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9328048603245422</v>
+        <v>-0.1602134241847393</v>
       </c>
     </row>
     <row r="5">
@@ -522,16 +522,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>103387.3941828218</v>
+        <v>135621.1514656016</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5692712692917075</v>
+        <v>0.08849131417298814</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5890607796826215</v>
+        <v>0.7853866396558743</v>
       </c>
       <c r="E5" t="n">
-        <v>-1</v>
+        <v>-0.1008841890743054</v>
       </c>
     </row>
     <row r="6">
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>108745.1679946647</v>
+        <v>129910.5786667173</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5692712692917075</v>
+        <v>0.08849131417298814</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5890607796826215</v>
+        <v>0.7853866396558743</v>
       </c>
       <c r="E6" t="n">
-        <v>-1</v>
+        <v>-0.06136110830894741</v>
       </c>
     </row>
   </sheetData>
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -606,19 +606,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>66488.87224966632</v>
+        <v>34243.97455063702</v>
       </c>
       <c r="C2" t="n">
-        <v>68766.10632519744</v>
+        <v>61607.21690378158</v>
       </c>
       <c r="D2" t="n">
-        <v>63191.25655201568</v>
+        <v>41400.01735499882</v>
       </c>
       <c r="E2" t="n">
-        <v>62188.22145529254</v>
+        <v>31818.65536020967</v>
       </c>
       <c r="F2" t="n">
-        <v>62456.66151250518</v>
+        <v>26108.0825613254</v>
       </c>
     </row>
     <row r="3">
@@ -628,19 +628,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19810.00361875292</v>
+        <v>32297.31385398124</v>
       </c>
       <c r="C3" t="n">
-        <v>22737.72379661772</v>
+        <v>27554.99749148169</v>
       </c>
       <c r="D3" t="n">
-        <v>15887.36880429244</v>
+        <v>27554.99749148169</v>
       </c>
       <c r="E3" t="n">
-        <v>14044.30996891527</v>
+        <v>27554.99749148169</v>
       </c>
       <c r="F3" t="n">
-        <v>16174.72141134232</v>
+        <v>27554.99749148169</v>
       </c>
     </row>
     <row r="4">
@@ -650,19 +650,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12172.28445731253</v>
+        <v>34678.53872393133</v>
       </c>
       <c r="C4" t="n">
-        <v>15272.55083458049</v>
+        <v>34678.53872393088</v>
       </c>
       <c r="D4" t="n">
-        <v>8343.637726546009</v>
+        <v>34678.53872393088</v>
       </c>
       <c r="E4" t="n">
-        <v>7788.703903100461</v>
+        <v>34678.53872393088</v>
       </c>
       <c r="F4" t="n">
-        <v>9289.49723605082</v>
+        <v>34678.53872393088</v>
       </c>
     </row>
     <row r="5">
@@ -672,19 +672,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35698.66526948559</v>
+        <v>29463.09716747679</v>
       </c>
       <c r="C5" t="n">
-        <v>33062.10426299669</v>
+        <v>26291.02206540454</v>
       </c>
       <c r="D5" t="n">
-        <v>21483.02892754934</v>
+        <v>26291.02206540454</v>
       </c>
       <c r="E5" t="n">
-        <v>19366.15885551354</v>
+        <v>26291.02206540454</v>
       </c>
       <c r="F5" t="n">
-        <v>20824.28783476638</v>
+        <v>26291.02206540454</v>
       </c>
     </row>
     <row r="6">
@@ -694,41 +694,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2568.91097435111</v>
+        <v>19434.85391947367</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>15277.93782457481</v>
       </c>
       <c r="D6" t="n">
-        <v>2248.76706754619</v>
+        <v>15277.93782457481</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>15277.93782457481</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A6</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2070.360612551229</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1537.391824255647</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
+        <v>15277.93782457481</v>
       </c>
     </row>
   </sheetData>
@@ -797,28 +775,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5624459457212084</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4999870658893482</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>25.00064670553259</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>74.99935329446741</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>386.2057834806377</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-231.7119547921885</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -826,28 +804,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4885964065546198</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4292189957726532</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>28.53905021136734</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>71.46094978863266</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>312.3301636111426</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-194.3049980419629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -855,28 +833,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.510942873719857</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4292189957726377</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>28.53905021136812</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>71.46094978863188</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>312.3262346915286</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-194.3049980419611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -884,28 +862,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5373902643481295</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4292189957726379</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>28.53905021136811</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>71.46094978863189</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>312.3197444640236</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-194.3049980419611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -913,28 +891,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.583216524623086</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4999870658900903</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>25.00064670549548</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>74.9993532945045</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>386.2007995714465</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-231.7119547922896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -942,28 +920,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9484810945203417</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.866559348766242</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>6.672032561687893</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>93.3279674383121</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>893.5626990292251</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-528.1751824214176</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -971,28 +949,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1.044229769881175</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7742983325936428</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9999999999999998</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>182.4527354399995</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-304.3097009888528</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1000,28 +978,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.8169625006017113</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7365441523844599</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>837.5872473204959</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-139.8953544970568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1029,28 +1007,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>1.238893016775156</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7292246311894153</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1608540987454164</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>58.04270493727082</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>41.95729506272918</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>559.5471120521648</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>128.800735898053</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1058,28 +1036,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>2.417950560127202</v>
+        <v>3.532530847396926</v>
       </c>
       <c r="C11" t="n">
-        <v>0.857983524411118</v>
+        <v>0.2306358242409365</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4506931797030318</v>
+        <v>-0.0562833676369127</v>
       </c>
       <c r="F11" t="n">
-        <v>72.53465898515159</v>
+        <v>47.18583161815436</v>
       </c>
       <c r="G11" t="n">
-        <v>27.46534101484841</v>
+        <v>52.81416838184563</v>
       </c>
       <c r="H11" t="n">
-        <v>620.0819227670872</v>
+        <v>-486.2362905051125</v>
       </c>
       <c r="I11" t="n">
-        <v>75.76450760779487</v>
+        <v>1209.376275252651</v>
       </c>
     </row>
     <row r="12">
@@ -1087,28 +1065,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>3.133309717572526</v>
+        <v>8.266650006244634</v>
       </c>
       <c r="C12" t="n">
+        <v>0.3033029825583616</v>
+      </c>
+      <c r="D12" t="n">
         <v>1</v>
       </c>
-      <c r="D12" t="n">
-        <v>0.9440313913561559</v>
-      </c>
       <c r="E12" t="n">
-        <v>0.7093278258359393</v>
+        <v>0.5447138968193286</v>
       </c>
       <c r="F12" t="n">
-        <v>85.46639129179697</v>
+        <v>77.23569484096643</v>
       </c>
       <c r="G12" t="n">
-        <v>14.53360870820303</v>
+        <v>22.76430515903357</v>
       </c>
       <c r="H12" t="n">
-        <v>277.231129021385</v>
+        <v>-1157.494114958183</v>
       </c>
       <c r="I12" t="n">
-        <v>150.024275542243</v>
+        <v>1120.966733563085</v>
       </c>
     </row>
     <row r="13">
@@ -1116,28 +1094,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>2.910778247959986</v>
+        <v>10.11358862402805</v>
       </c>
       <c r="C13" t="n">
+        <v>0.3322949008468301</v>
+      </c>
+      <c r="D13" t="n">
         <v>1</v>
       </c>
-      <c r="D13" t="n">
-        <v>0.8299450522791015</v>
-      </c>
       <c r="E13" t="n">
-        <v>-0.7252011201764965</v>
+        <v>0.4450400887456926</v>
       </c>
       <c r="F13" t="n">
-        <v>13.73994399117517</v>
+        <v>72.25200443728464</v>
       </c>
       <c r="G13" t="n">
-        <v>86.26005600882482</v>
+        <v>27.74799556271537</v>
       </c>
       <c r="H13" t="n">
-        <v>2839.910443724124</v>
+        <v>-1425.423635533201</v>
       </c>
       <c r="I13" t="n">
-        <v>-508.3008688358131</v>
+        <v>916.9385802818665</v>
       </c>
     </row>
     <row r="14">
@@ -1145,28 +1123,28 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>2.773646437750525</v>
+        <v>11.59034282110254</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9999999999999999</v>
+        <v>0.3938301517104429</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7515628027201066</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6399447465724917</v>
+        <v>0.06279997838788981</v>
       </c>
       <c r="F14" t="n">
-        <v>18.00276267137542</v>
+        <v>53.13999891939449</v>
       </c>
       <c r="G14" t="n">
-        <v>81.99723732862459</v>
+        <v>46.86000108060551</v>
       </c>
       <c r="H14" t="n">
-        <v>2268.162380454639</v>
+        <v>-1642.073825936403</v>
       </c>
       <c r="I14" t="n">
-        <v>-457.6556333437726</v>
+        <v>484.4319868237744</v>
       </c>
     </row>
     <row r="15">
@@ -1174,28 +1152,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>3.032617011177051</v>
+        <v>11.38772509545866</v>
       </c>
       <c r="C15" t="n">
+        <v>0.4111881536261818</v>
+      </c>
+      <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="D15" t="n">
-        <v>0.7804418583307924</v>
-      </c>
       <c r="E15" t="n">
-        <v>-0.9999719986096078</v>
+        <v>0.07378912408210732</v>
       </c>
       <c r="F15" t="n">
-        <v>0.001400069519602803</v>
+        <v>53.68945620410537</v>
       </c>
       <c r="G15" t="n">
-        <v>99.9985999304804</v>
+        <v>46.31054379589464</v>
       </c>
       <c r="H15" t="n">
-        <v>3412.619936526687</v>
+        <v>-1612.215511418181</v>
       </c>
       <c r="I15" t="n">
-        <v>-661.4489907695992</v>
+        <v>403.4630157730165</v>
       </c>
     </row>
     <row r="16">
@@ -1203,28 +1181,28 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>3.063083185734643</v>
+        <v>7.842862055010452</v>
       </c>
       <c r="C16" t="n">
+        <v>0.2878037006788998</v>
+      </c>
+      <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="D16" t="n">
-        <v>0.8292485422201399</v>
-      </c>
       <c r="E16" t="n">
-        <v>0.7025551758308846</v>
+        <v>0.04819942791556583</v>
       </c>
       <c r="F16" t="n">
-        <v>85.12775879154422</v>
+        <v>52.4099713957783</v>
       </c>
       <c r="G16" t="n">
-        <v>14.87224120845577</v>
+        <v>47.59002860422171</v>
       </c>
       <c r="H16" t="n">
-        <v>222.2007410035829</v>
+        <v>-1096.448802051681</v>
       </c>
       <c r="I16" t="n">
-        <v>139.5404412843162</v>
+        <v>646.9796104832997</v>
       </c>
     </row>
     <row r="17">
@@ -1232,28 +1210,28 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>3.281944431504254</v>
+        <v>1.880353385306708</v>
       </c>
       <c r="C17" t="n">
+        <v>0.1878771421528856</v>
+      </c>
+      <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.9703931355941023</v>
-      </c>
       <c r="E17" t="n">
-        <v>0.5999741845716707</v>
+        <v>-0.06116695464953887</v>
       </c>
       <c r="F17" t="n">
-        <v>79.99870922858354</v>
+        <v>46.94165226752306</v>
       </c>
       <c r="G17" t="n">
-        <v>20.00129077141646</v>
+        <v>53.05834773247695</v>
       </c>
       <c r="H17" t="n">
-        <v>439.6967896917781</v>
+        <v>-257.2683742379943</v>
       </c>
       <c r="I17" t="n">
-        <v>81.50814172369971</v>
+        <v>1033.542712981327</v>
       </c>
     </row>
     <row r="18">
@@ -1261,28 +1239,28 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>1.855773656675085</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7799942942880668</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9999999999999999</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4625121877503209</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>73.12560938751605</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>26.87439061248395</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>489.2809228670089</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>133.321606076177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1290,28 +1268,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.3727327307205366</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.659082616645565</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9999999999999999</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2728552497273139</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>63.6427624863657</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>36.3572375136343</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>223.2821850024586</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>379.1092377104039</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1319,28 +1297,28 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.6246943150497889</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5685501428830233</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.08775149855228241</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>45.61242507238588</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>54.38757492761412</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>326.4915965441656</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>145.9036729747903</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1348,28 +1326,28 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.877615565053756</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4427100869313471</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.008121506881702635</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>50.40607534408513</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>49.59392465591487</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>396.8458967453635</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>-39.63988449551054</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1377,28 +1355,28 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.739566240552067</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5073270815837161</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.09345895699468423</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>54.67294784973421</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>45.32705215026579</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>298.5738460818336</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>12.07463031357074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1406,28 +1384,28 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>1.14122721723133</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8054428762131615</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6461159005504926</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>82.30579502752464</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>17.69420497247537</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>102.4886731393838</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>-107.6218115774053</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1435,28 +1413,28 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9364795040944236</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5001430068316975</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>24.99284965841513</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>75.00715034158489</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>582.2832380022438</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>-347.5998255914813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1464,28 +1442,28 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.8999999999999999</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9999999999999998</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6426310240088519</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.5554777833531442</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>22.22611083234278</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>77.77388916765722</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>470.2012422398208</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>-269.1877668165117</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1499,7 +1477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1513,13 +1491,47 @@
           <t>Spread_C4_kWh</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>W_sellers_total_uo</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>W_buyers_total_uo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>W_total_uo</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Nota_W</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.2165847181327795</v>
+        <v>0.1346089702964729</v>
       </c>
       <c r="B2" t="n">
-        <v>14.46541230822103</v>
+        <v>20.3411259094923</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-7677.160554640755</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5815.69891515902</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-1861.461639481735</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>u.o.=unidades optimizacion; no son COP</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/resultados_comparacion.xlsx
+++ b/resultados_comparacion.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Ganancia_neta_COP</t>
+          <t>Ganancia_neta_$</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -465,16 +465,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>150117.7782155001</v>
+        <v>149166.3554244795</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1126722937529999</v>
+        <v>0.9032746487033748</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0.9346750792679107</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1510131705234475</v>
+        <v>-0.1983322631223311</v>
       </c>
     </row>
     <row r="3">
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>165409.7130091735</v>
+        <v>139838.4852193923</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08849131417298814</v>
+        <v>0.5778404947855829</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7853866396558743</v>
+        <v>0.5979278960648478</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2628055550044501</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4">
@@ -503,16 +503,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>145202.5134603907</v>
+        <v>116457.2612184539</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08849131417298814</v>
+        <v>0.5778404947855829</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7853866396558743</v>
+        <v>0.5979278960648478</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1602134241847393</v>
+        <v>-0.8991894959514061</v>
       </c>
     </row>
     <row r="5">
@@ -522,16 +522,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>135621.1514656016</v>
+        <v>104717.1460149028</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08849131417298814</v>
+        <v>0.5778404947855829</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7853866396558743</v>
+        <v>0.5979278960648478</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1008841890743054</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>129910.5786667173</v>
+        <v>103895.6403405108</v>
       </c>
       <c r="C6" t="n">
-        <v>0.08849131417298814</v>
+        <v>0.5778404947855829</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7853866396558743</v>
+        <v>0.5979278960648478</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.06136110830894741</v>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -606,19 +606,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34243.97455063702</v>
+        <v>69557.69058363501</v>
       </c>
       <c r="C2" t="n">
-        <v>61607.21690378158</v>
+        <v>68766.10632519744</v>
       </c>
       <c r="D2" t="n">
-        <v>41400.01735499882</v>
+        <v>63733.32234452738</v>
       </c>
       <c r="E2" t="n">
-        <v>31818.65536020967</v>
+        <v>62647.42656579717</v>
       </c>
       <c r="F2" t="n">
-        <v>26108.0825613254</v>
+        <v>62179.90670261838</v>
       </c>
     </row>
     <row r="3">
@@ -628,19 +628,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32297.31385398124</v>
+        <v>19171.76116172001</v>
       </c>
       <c r="C3" t="n">
-        <v>27554.99749148169</v>
+        <v>22737.72379661772</v>
       </c>
       <c r="D3" t="n">
-        <v>27554.99749148169</v>
+        <v>16134.25415423884</v>
       </c>
       <c r="E3" t="n">
-        <v>27554.99749148169</v>
+        <v>14165.09686728195</v>
       </c>
       <c r="F3" t="n">
-        <v>27554.99749148169</v>
+        <v>14072.01195558244</v>
       </c>
     </row>
     <row r="4">
@@ -650,19 +650,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34678.53872393133</v>
+        <v>10632.28411977585</v>
       </c>
       <c r="C4" t="n">
-        <v>34678.53872393088</v>
+        <v>15272.55083458049</v>
       </c>
       <c r="D4" t="n">
-        <v>34678.53872393088</v>
+        <v>9133.044143474433</v>
       </c>
       <c r="E4" t="n">
-        <v>34678.53872393088</v>
+        <v>8538.463706013774</v>
       </c>
       <c r="F4" t="n">
-        <v>34678.53872393088</v>
+        <v>9200.804361307739</v>
       </c>
     </row>
     <row r="5">
@@ -672,19 +672,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29463.09716747679</v>
+        <v>46460.81498385874</v>
       </c>
       <c r="C5" t="n">
-        <v>26291.02206540454</v>
+        <v>33062.10426299668</v>
       </c>
       <c r="D5" t="n">
-        <v>26291.02206540454</v>
+        <v>21586.58297443768</v>
       </c>
       <c r="E5" t="n">
-        <v>26291.02206540454</v>
+        <v>19366.15887580989</v>
       </c>
       <c r="F5" t="n">
-        <v>26291.02206540454</v>
+        <v>18442.91732100224</v>
       </c>
     </row>
     <row r="6">
@@ -694,19 +694,41 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19434.85391947367</v>
+        <v>1664.661629266838</v>
       </c>
       <c r="C6" t="n">
-        <v>15277.93782457481</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>15277.93782457481</v>
+        <v>3396.302388271019</v>
       </c>
       <c r="E6" t="n">
-        <v>15277.93782457481</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>15277.93782457481</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1679.14294622309</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2473.755213504526</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -775,28 +797,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.9399999400338928</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.6686857048282192</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-0.9999998871911312</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>5.640443442246002e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>99.99999435955655</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-372.2898112209105</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-352.3681535425844</v>
       </c>
     </row>
     <row r="3">
@@ -804,28 +826,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.819999943655227</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.5802082045347263</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-0.9999999668484872</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1.657575637444197e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>99.99999834242436</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-280.1173348421868</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-307.3849946240268</v>
       </c>
     </row>
     <row r="4">
@@ -833,28 +855,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.8199999436594572</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.6067446330092739</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-0.9999999668470195</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1.657649028671462e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>99.99999834235098</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-294.2727143408214</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-307.3849946254074</v>
       </c>
     </row>
     <row r="5">
@@ -862,28 +884,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.8199999436690311</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.6381509078540631</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-0.9999999668445049</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.657774758114215e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>99.99999834222524</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-309.5313015559924</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-307.3849946286449</v>
       </c>
     </row>
     <row r="6">
@@ -891,28 +913,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>0.9399999400248249</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.6933796137848025</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-0.9999998871817479</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>5.640912613375778e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>99.9999943590874</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-383.5647415046785</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-352.3681535376822</v>
       </c>
     </row>
     <row r="7">
@@ -920,28 +942,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1.392088421217931</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.8865130594912339</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0.5225055042848792</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>23.87472478575604</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>76.12527521424396</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-745.9715435404396</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-408.547157976501</v>
       </c>
     </row>
     <row r="8">
@@ -949,28 +971,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1.417903162479265</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.9496111253101039</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-1612.767297759848</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-410.7494349483037</v>
       </c>
     </row>
     <row r="9">
@@ -978,28 +1000,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1.496962380900113</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.913543094052895</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>-0.762286730110183</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>11.88566349449085</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>88.11433650550916</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-1030.530138898106</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-334.1509424896282</v>
       </c>
     </row>
     <row r="10">
@@ -1007,28 +1029,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1.823122656166763</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.9048772389131633</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-0.4470690083572017</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>27.64654958213992</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>72.35345041786007</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-640.9005166264891</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-370.7146991209874</v>
       </c>
     </row>
     <row r="11">
@@ -1036,28 +1058,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3.532530847396926</v>
+        <v>2.237950589074116</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2306358242409365</v>
+        <v>0.9299434223848493</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0562833676369127</v>
+        <v>0.4489013975025599</v>
       </c>
       <c r="F11" t="n">
-        <v>47.18583161815436</v>
+        <v>72.445069875128</v>
       </c>
       <c r="G11" t="n">
-        <v>52.81416838184563</v>
+        <v>27.554930124872</v>
       </c>
       <c r="H11" t="n">
-        <v>-486.2362905051125</v>
+        <v>-235.9398716672053</v>
       </c>
       <c r="I11" t="n">
-        <v>1209.376275252651</v>
+        <v>98.05096264762204</v>
       </c>
     </row>
     <row r="12">
@@ -1065,28 +1087,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>8.266650006244634</v>
+        <v>3.439461603981111</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3033029825583616</v>
+        <v>0.9020098936947899</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5447138968193286</v>
+        <v>0.3700826874666402</v>
       </c>
       <c r="F12" t="n">
-        <v>77.23569484096643</v>
+        <v>68.50413437333201</v>
       </c>
       <c r="G12" t="n">
-        <v>22.76430515903357</v>
+        <v>31.49586562666799</v>
       </c>
       <c r="H12" t="n">
-        <v>-1157.494114958183</v>
+        <v>-400.8616662481227</v>
       </c>
       <c r="I12" t="n">
-        <v>1120.966733563085</v>
+        <v>-74.41598735084293</v>
       </c>
     </row>
     <row r="13">
@@ -1094,28 +1116,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>10.11358862402805</v>
+        <v>4.10301821050562</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3322949008468301</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0.9791783607854583</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4450400887456926</v>
+        <v>0.5335703135392378</v>
       </c>
       <c r="F13" t="n">
-        <v>72.25200443728464</v>
+        <v>76.67851567696188</v>
       </c>
       <c r="G13" t="n">
-        <v>27.74799556271537</v>
+        <v>23.32148432303811</v>
       </c>
       <c r="H13" t="n">
-        <v>-1425.423635533201</v>
+        <v>-489.513598027426</v>
       </c>
       <c r="I13" t="n">
-        <v>916.9385802818665</v>
+        <v>-57.16303604939945</v>
       </c>
     </row>
     <row r="14">
@@ -1123,28 +1145,28 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>11.59034282110254</v>
+        <v>3.679416446228168</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3938301517104429</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.8970576253933392</v>
       </c>
       <c r="E14" t="n">
-        <v>0.06279997838788981</v>
+        <v>0.6161853741023305</v>
       </c>
       <c r="F14" t="n">
-        <v>53.13999891939449</v>
+        <v>80.80926870511652</v>
       </c>
       <c r="G14" t="n">
-        <v>46.86000108060551</v>
+        <v>19.19073129488347</v>
       </c>
       <c r="H14" t="n">
-        <v>-1642.073825936403</v>
+        <v>-395.4822538578713</v>
       </c>
       <c r="I14" t="n">
-        <v>484.4319868237744</v>
+        <v>36.50989633551531</v>
       </c>
     </row>
     <row r="15">
@@ -1152,28 +1174,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>11.38772509545866</v>
+        <v>4.276429554510765</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4111881536261818</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0.9294215164577244</v>
       </c>
       <c r="E15" t="n">
-        <v>0.07378912408210732</v>
+        <v>0.5016611875080279</v>
       </c>
       <c r="F15" t="n">
-        <v>53.68945620410537</v>
+        <v>75.08305937540139</v>
       </c>
       <c r="G15" t="n">
-        <v>46.31054379589464</v>
+        <v>24.9169406245986</v>
       </c>
       <c r="H15" t="n">
-        <v>-1612.215511418181</v>
+        <v>-517.0999052847625</v>
       </c>
       <c r="I15" t="n">
-        <v>403.4630157730165</v>
+        <v>-131.920529389885</v>
       </c>
     </row>
     <row r="16">
@@ -1181,28 +1203,28 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>7.842862055010452</v>
+        <v>4.350745143257377</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2878037006788998</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0.98138060402169</v>
       </c>
       <c r="E16" t="n">
-        <v>0.04819942791556583</v>
+        <v>0.5009141549904218</v>
       </c>
       <c r="F16" t="n">
-        <v>52.4099713957783</v>
+        <v>75.04570774952109</v>
       </c>
       <c r="G16" t="n">
-        <v>47.59002860422171</v>
+        <v>24.9542922504789</v>
       </c>
       <c r="H16" t="n">
-        <v>-1096.448802051681</v>
+        <v>-569.8999782549944</v>
       </c>
       <c r="I16" t="n">
-        <v>646.9796104832997</v>
+        <v>-119.0252889707308</v>
       </c>
     </row>
     <row r="17">
@@ -1210,28 +1232,28 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>1.880353385306708</v>
+        <v>3.358229955435879</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1878771421528856</v>
+        <v>0.8816705225208304</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.06116695464953887</v>
+        <v>0.8050010926168463</v>
       </c>
       <c r="F17" t="n">
-        <v>46.94165226752306</v>
+        <v>90.25005463084231</v>
       </c>
       <c r="G17" t="n">
-        <v>53.05834773247695</v>
+        <v>9.749945369157679</v>
       </c>
       <c r="H17" t="n">
-        <v>-257.2683742379943</v>
+        <v>-445.5088447732496</v>
       </c>
       <c r="I17" t="n">
-        <v>1033.542712981327</v>
+        <v>191.0635893751935</v>
       </c>
     </row>
     <row r="18">
@@ -1239,28 +1261,28 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>2.020003288577634</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.936418766552147</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-0.4545285352714353</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>27.27357323642823</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>72.72642676357177</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-294.4701895372156</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-293.4866547539098</v>
       </c>
     </row>
     <row r="19">
@@ -1268,28 +1290,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.572732682271398</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.8137926067306609</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>0.6735662474513869</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>83.67831237256935</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>16.32168762743066</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-54.69000408611848</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>389.1339941172304</v>
       </c>
     </row>
     <row r="20">
@@ -1297,28 +1319,28 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.6446942833678948</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.6971857962676258</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.5555998764593696</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>77.77999382296848</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>22.22000617703152</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>-81.04701299952464</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>234.3017010337495</v>
       </c>
     </row>
     <row r="21">
@@ -1326,28 +1348,28 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>0.8776155650537559</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.5419237956168438</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.4581106084246955</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>72.90553042123477</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>27.09446957876522</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>-110.4286908828075</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>50.09677675034703</v>
       </c>
     </row>
     <row r="22">
@@ -1355,28 +1377,28 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>0.7395662405520669</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.6212167895658525</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.7624415905876064</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>88.12207952938031</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>11.87792047061968</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>-93.01355269698928</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>124.5049810738735</v>
       </c>
     </row>
     <row r="23">
@@ -1384,28 +1406,28 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1.541227153157251</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.820163757030747</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>-0.9999999717508008</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1.412459960844969e-06</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>99.99999858754005</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>-601.1563832675619</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>-577.7440656052258</v>
       </c>
     </row>
     <row r="24">
@@ -1413,28 +1435,28 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>1.083138434494439</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.8981739860870275</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>-0.7996195567157519</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>10.0190221642124</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>89.9809778357876</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>-339.5742514868742</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>-369.0338071114764</v>
       </c>
     </row>
     <row r="25">
@@ -1442,28 +1464,28 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>1.059999935996569</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>0.7650368998564695</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>-0.9999998641819269</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>6.790903660779226e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>99.99999320909635</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>-462.2653405584261</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>-397.3513192799177</v>
       </c>
     </row>
   </sheetData>
@@ -1483,7 +1505,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PoF_P2P_vs_C4</t>
+          <t>RPE_P2P_vs_C4</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -1514,19 +1536,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.1346089702964729</v>
+        <v>0.3034914606255735</v>
       </c>
       <c r="B2" t="n">
-        <v>20.3411259094923</v>
+        <v>14.16391272090346</v>
       </c>
       <c r="C2" t="n">
-        <v>-7677.160554640755</v>
+        <v>-10760.89694391862</v>
       </c>
       <c r="D2" t="n">
-        <v>5815.69891515902</v>
+        <v>-4047.532312671623</v>
       </c>
       <c r="E2" t="n">
-        <v>-1861.461639481735</v>
+        <v>-14808.42925659025</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
